--- a/stufe-5/dok/migrate-ig-to-ig-publisher-ptdata-1969/observations-summary.xlsx
+++ b/stufe-5/dok/migrate-ig-to-ig-publisher-ptdata-1969/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Profile</t>
   </si>
@@ -45,57 +45,6 @@
   </si>
   <si>
     <t>Method</t>
-  </si>
-  <si>
-    <t>ISiKAlkoholAbusus</t>
-  </si>
-  <si>
-    <t>ISiK Alkohol Abusus</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#social-history</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>null#15167005, null#74043-1</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
-  </si>
-  <si>
-    <t>dateTimeĵ, Periodĵ</t>
-  </si>
-  <si>
-    <t>CodeableConceptĵ</t>
-  </si>
-  <si>
-    <t>optional</t>
-  </si>
-  <si>
-    <t>ISiKRaucherStatus</t>
-  </si>
-  <si>
-    <t>ISiK Raucherstatus</t>
-  </si>
-  <si>
-    <t>null#77176002, null#72166-2</t>
-  </si>
-  <si>
-    <t>ISiKSchwangerschaftsstatus</t>
-  </si>
-  <si>
-    <t>ISiK Schwangerschaftsstatus</t>
-  </si>
-  <si>
-    <t>LOINC#82810-3</t>
-  </si>
-  <si>
-    <t>ISiKStillstatus</t>
-  </si>
-  <si>
-    <t>null#413712001, null#63895-7</t>
   </si>
 </sst>
 </file>
@@ -229,7 +178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -267,146 +216,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K2" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K3" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K4" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="F5" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J5" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K5" t="s" s="2">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
